--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -548,8 +548,60 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-01 06:50:02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>673.83</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>673.83</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>678.28</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026/09/01 06:50:02</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:25:55</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J2"/>
+  <autoFilter ref="A1:J3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -612,7 +664,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>678.28</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -600,8 +600,60 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:55:58</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>670.82</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>670.82</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>673.65</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>673.65</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>678.09</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026/09/01 09:55:58</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:58:31</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J3"/>
+  <autoFilter ref="A1:J4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -664,13 +716,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>678.28</v>
+        <v>678.2166999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>678.28</v>
+        <v>678.09</v>
       </c>
       <c r="E4" t="n">
         <v>678.28</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,8 +652,60 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:35:59</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>671.01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>671.01</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>673.84</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>673.84</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>678.09</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026/09/01 15:35:59</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-09-01 07:40:33</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J4"/>
+  <autoFilter ref="A1:J5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -716,10 +768,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>678.2166999999999</v>
+        <v>678.1849999999999</v>
       </c>
       <c r="D4" t="n">
         <v>678.09</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -704,8 +704,60 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-01 20:41:01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>671.03</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>671.03</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>673.86</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>673.86</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>678.09</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026/09/01 20:41:01</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-09-01 12:45:31</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J5"/>
+  <autoFilter ref="A1:J6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -768,10 +820,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>678.1849999999999</v>
+        <v>678.1660000000001</v>
       </c>
       <c r="D4" t="n">
         <v>678.09</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -756,8 +756,60 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:56:02</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>670.88</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>670.88</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>673.71</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>673.71</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>678.09</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026/09/02 00:56:02</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-01 16:58:31</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J6"/>
+  <autoFilter ref="A1:J7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -768,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -832,61 +884,102 @@
         <v>678.28</v>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>678.09</v>
+      </c>
+      <c r="D5" t="n">
+        <v>678.09</v>
+      </c>
+      <c r="E5" t="n">
+        <v>678.09</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>firstPublishTime</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>middle</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>publishTimeRaw</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-09-01 02:50:03</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>678.28</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:56:02</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>678.09</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026/09/02 00:56:02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -808,8 +808,60 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-02 02:50:46</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>671.05</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>671.05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>673.88</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>673.88</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>678.09</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026/09/02 02:50:46</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-01 19:50:27</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J7"/>
+  <autoFilter ref="A1:J8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -891,7 +943,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>678.09</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -860,8 +860,60 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-02 05:30:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>671.05</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>671.05</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>673.88</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>673.88</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>678.09</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026/09/02 05:30:00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-01 22:09:03</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J8"/>
+  <autoFilter ref="A1:J9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -943,7 +995,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
         <v>678.09</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -912,8 +912,60 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-02 07:49:21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>671.05</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>671.05</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>673.88</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>673.88</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>678.09</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026/09/02 07:49:21</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:13:11</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J9"/>
+  <autoFilter ref="A1:J10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -995,7 +1047,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
         <v>678.09</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -964,8 +964,60 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:36:04</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>671.05</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>671.05</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>673.88</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>673.88</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>678.29</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026/09/02 12:36:04</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:41:04</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J10"/>
+  <autoFilter ref="A1:J11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1047,16 +1099,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>678.09</v>
+        <v>678.13</v>
       </c>
       <c r="D5" t="n">
         <v>678.09</v>
       </c>
       <c r="E5" t="n">
-        <v>678.09</v>
+        <v>678.29</v>
       </c>
     </row>
     <row r="6"/>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1016,8 +1016,60 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:01:05</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>671.06</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>671.06</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>673.89</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>673.89</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>678.29</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026/09/02 17:01:05</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:04:45</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J11"/>
+  <autoFilter ref="A1:J12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1099,10 +1151,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>678.13</v>
+        <v>678.1567</v>
       </c>
       <c r="D5" t="n">
         <v>678.09</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1068,8 +1068,60 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-02 21:34:06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>670.81</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>670.81</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>673.64</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>673.64</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>678.29</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026/09/02 21:34:06</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:35:13</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J12"/>
+  <autoFilter ref="A1:J13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1151,10 +1203,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>678.1567</v>
+        <v>678.1757</v>
       </c>
       <c r="D5" t="n">
         <v>678.09</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1120,8 +1120,60 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-03 01:16:07</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>670.72</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>670.72</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>673.55</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>673.55</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>678.29</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026/09/03 01:16:07</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:18:47</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J13"/>
+  <autoFilter ref="A1:J14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1132,7 +1184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1215,83 +1267,124 @@
         <v>678.29</v>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>678.29</v>
+      </c>
+      <c r="D6" t="n">
+        <v>678.29</v>
+      </c>
+      <c r="E6" t="n">
+        <v>678.29</v>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-01 02:50:03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>678.28</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026/09/01 02:50:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-09-02 00:56:02</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>678.09</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-03 01:16:07</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>678.29</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026/09/03 01:16:07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:E6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1172,8 +1172,60 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-03 02:50:43</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>673.83</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>673.83</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>678.29</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026/09/03 02:50:43</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-02 19:52:52</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J14"/>
+  <autoFilter ref="A1:J15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1274,7 +1326,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>678.29</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1224,8 +1224,60 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-03 05:30:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>673.83</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>673.83</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>678.29</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026/09/03 05:30:00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-02 22:15:57</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J15"/>
+  <autoFilter ref="A1:J16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1326,7 +1378,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
         <v>678.29</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1276,8 +1276,60 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-03 07:50:27</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>673.83</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>673.83</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>678.29</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026/09/03 07:50:27</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:20:40</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J16"/>
+  <autoFilter ref="A1:J17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1378,7 +1430,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
         <v>678.29</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1328,8 +1328,60 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:41:10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>670.74</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>670.74</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>673.57</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>673.57</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>678.07</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026/09/03 12:41:10</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:47:00</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J17"/>
+  <autoFilter ref="A1:J18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1430,13 +1482,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>678.29</v>
+        <v>678.246</v>
       </c>
       <c r="D6" t="n">
-        <v>678.29</v>
+        <v>678.0700000000001</v>
       </c>
       <c r="E6" t="n">
         <v>678.29</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1380,8 +1380,60 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:11:11</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>670.75</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>670.75</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>673.58</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>673.58</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>678.07</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026/09/03 17:11:11</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:13:49</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J18"/>
+  <autoFilter ref="A1:J19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1482,10 +1534,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>678.246</v>
+        <v>678.2166999999999</v>
       </c>
       <c r="D6" t="n">
         <v>678.0700000000001</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1432,8 +1432,60 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-03 21:31:12</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>670.75</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>670.75</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>673.58</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>673.58</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>678.07</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026/09/03 21:31:12</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:37:46</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J19"/>
+  <autoFilter ref="A1:J20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1534,10 +1586,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>678.2166999999999</v>
+        <v>678.1957</v>
       </c>
       <c r="D6" t="n">
         <v>678.0700000000001</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1484,8 +1484,60 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-04 01:11:13</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>670.75</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>670.75</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>673.58</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>673.58</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>678.07</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026/09/04 01:11:13</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:13:45</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J20"/>
+  <autoFilter ref="A1:J21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1496,7 +1548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1598,105 +1650,146 @@
         <v>678.29</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>678.0700000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>678.0700000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>678.0700000000001</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:56:02</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>678.09</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026/09/02 00:56:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>2026-09-03 01:16:07</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>678.29</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-04 01:11:13</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>678.07</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026/09/04 01:11:13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <autoFilter ref="A1:E7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1536,8 +1536,60 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:49:45</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>670.97</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>670.97</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>673.8</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>673.8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>678.07</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026/09/04 02:49:45</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-03 19:53:41</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J21"/>
+  <autoFilter ref="A1:J22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1657,7 +1709,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>678.0700000000001</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1588,8 +1588,60 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-04 05:30:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>670.97</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>670.97</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>673.8</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>673.8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>678.07</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026/09/04 05:30:00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-03 22:15:04</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J22"/>
+  <autoFilter ref="A1:J23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1709,7 +1761,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>678.0700000000001</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1640,8 +1640,60 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-04 07:52:26</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>670.97</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>670.97</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>673.8</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>673.8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>678.07</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026/09/04 07:52:26</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-04 00:09:08</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J23"/>
+  <autoFilter ref="A1:J24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1761,7 +1813,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
         <v>678.0700000000001</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1692,8 +1692,60 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:26:16</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>670.52</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>670.52</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>673.35</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>673.35</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026/09/04 12:26:16</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:31:57</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J24"/>
+  <autoFilter ref="A1:J25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1813,13 +1865,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>678.0700000000001</v>
+        <v>678.03</v>
       </c>
       <c r="D7" t="n">
-        <v>678.0700000000001</v>
+        <v>677.87</v>
       </c>
       <c r="E7" t="n">
         <v>678.0700000000001</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1744,8 +1744,60 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-04 16:56:17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>669.99</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>669.99</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>672.81</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>672.81</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026/09/04 16:56:17</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:00:49</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J25"/>
+  <autoFilter ref="A1:J26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1865,10 +1917,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>678.03</v>
+        <v>678.0033</v>
       </c>
       <c r="D7" t="n">
         <v>677.87</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1796,8 +1796,60 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-04 21:21:18</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>670.09</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>670.09</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>672.91</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>672.91</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026/09/04 21:21:18</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-09-04 13:25:27</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J26"/>
+  <autoFilter ref="A1:J27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1917,10 +1969,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>678.0033</v>
+        <v>677.9843</v>
       </c>
       <c r="D7" t="n">
         <v>677.87</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1848,8 +1848,60 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-05 00:51:19</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>670.01</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>670.01</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>672.83</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>672.83</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026/09/05 00:51:19</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-09-04 16:57:05</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J27"/>
+  <autoFilter ref="A1:J28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1860,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1981,127 +2033,168 @@
         <v>678.0700000000001</v>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>677.87</v>
+      </c>
+      <c r="D8" t="n">
+        <v>677.87</v>
+      </c>
+      <c r="E8" t="n">
+        <v>677.87</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-03 01:16:07</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>678.29</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026/09/03 01:16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2026-09-04 01:11:13</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>678.07</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-05 00:51:19</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026/09/05 00:51:19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E7"/>
+  <autoFilter ref="A1:E8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1900,8 +1900,60 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-05 02:49:35</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026/09/05 02:49:35</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-09-04 19:22:01</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J28"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2040,7 +2092,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
         <v>677.87</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1952,8 +1952,60 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-05 05:30:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026/09/05 05:30:00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-09-04 21:36:41</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2092,7 +2144,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
         <v>677.87</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2004,8 +2004,60 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:30:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026/09/05 10:30:00</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-09-05 05:43:17</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2144,7 +2196,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
         <v>677.87</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2056,8 +2056,60 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-06 00:00:05</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026/09/06 00:00:05</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-09-05 17:54:50</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2068,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2208,149 +2260,190 @@
         <v>677.87</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>677.87</v>
+      </c>
+      <c r="D9" t="n">
+        <v>677.87</v>
+      </c>
+      <c r="E9" t="n">
+        <v>677.87</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-04 01:11:13</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>678.07</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026/09/04 01:11:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-09-05 00:51:19</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>677.87</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-06 00:00:05</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026/09/06 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2108,8 +2108,60 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-06 05:30:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026/09/06 05:30:00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:01:38</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J32"/>
+  <autoFilter ref="A1:J33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2267,7 +2319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>677.87</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2160,8 +2160,60 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:30:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026/09/06 10:30:00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-09-06 06:10:30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J33"/>
+  <autoFilter ref="A1:J34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2319,7 +2371,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>677.87</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2212,8 +2212,60 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-07 00:00:05</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026/09/07 00:00:05</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-09-06 16:59:11</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J34"/>
+  <autoFilter ref="A1:J35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2224,7 +2276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2383,171 +2435,212 @@
         <v>677.87</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>677.87</v>
+      </c>
+      <c r="D10" t="n">
+        <v>677.87</v>
+      </c>
+      <c r="E10" t="n">
+        <v>677.87</v>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-05 00:51:19</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026/09/05 00:51:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2026-09-06 00:00:05</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>677.87</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-07 00:00:05</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/09/07 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2264,8 +2264,60 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-07 05:30:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026/09/07 05:30:00</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-09-06 22:55:14</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J35"/>
+  <autoFilter ref="A1:J36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2442,7 +2494,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
         <v>677.87</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2316,8 +2316,60 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-07 08:31:29</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>670.13</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>672.95</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026/09/07 08:31:29</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-09-07 00:44:25</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J36"/>
+  <autoFilter ref="A1:J37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2494,7 +2546,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>677.87</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2368,8 +2368,60 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:11:34</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>669.98</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>669.98</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>672.8</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>672.8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>677.95</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026/09/07 13:11:34</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-09-07 05:16:16</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J37"/>
+  <autoFilter ref="A1:J38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2546,16 +2598,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>677.87</v>
+        <v>677.89</v>
       </c>
       <c r="D10" t="n">
         <v>677.87</v>
       </c>
       <c r="E10" t="n">
-        <v>677.87</v>
+        <v>677.95</v>
       </c>
     </row>
     <row r="11"/>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2420,8 +2420,60 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-07 18:26:35</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>669.89</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>669.89</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>672.71</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>672.71</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>677.95</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026/09/07 18:26:35</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-09-07 10:28:12</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J38"/>
+  <autoFilter ref="A1:J39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2598,10 +2650,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>677.89</v>
+        <v>677.902</v>
       </c>
       <c r="D10" t="n">
         <v>677.87</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2472,8 +2472,60 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-07 23:56:36</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>669.91</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>669.91</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>672.73</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>672.73</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>677.95</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026/09/07 23:56:36</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-09-07 16:00:42</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J39"/>
+  <autoFilter ref="A1:J40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2650,10 +2702,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>677.902</v>
+        <v>677.91</v>
       </c>
       <c r="D10" t="n">
         <v>677.87</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2524,8 +2524,60 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-08 02:50:02</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>670.01</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>670.01</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>672.83</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>672.83</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>677.95</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026/09/08 02:50:02</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-09-07 19:52:07</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J40"/>
+  <autoFilter ref="A1:J41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2536,7 +2588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2714,156 +2766,153 @@
         <v>677.95</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>677.95</v>
+      </c>
+      <c r="D11" t="n">
+        <v>677.95</v>
+      </c>
+      <c r="E11" t="n">
+        <v>677.95</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2873,34 +2922,78 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-06 00:00:05</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/09/06 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>2026-09-07 00:00:05</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>677.87</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-08 02:50:02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>677.95</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/09/08 02:50:02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2576,8 +2576,60 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-08 05:30:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>670.01</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>670.01</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>672.83</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>672.83</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>677.95</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026/09/08 05:30:00</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:25:35</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J41"/>
+  <autoFilter ref="A1:J42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2773,7 +2825,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>677.95</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2628,8 +2628,60 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-08 08:28:59</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>670.01</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>670.01</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>672.83</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>672.83</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>677.95</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026/09/08 08:28:59</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:36:14</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J42"/>
+  <autoFilter ref="A1:J43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2825,7 +2877,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>677.95</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2680,8 +2680,60 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:11:39</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>669.88</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>669.88</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>672.7</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>672.7</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>678.04</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026/09/08 13:11:39</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-09-08 05:12:56</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J43"/>
+  <autoFilter ref="A1:J44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2877,16 +2929,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>677.95</v>
+        <v>677.9725</v>
       </c>
       <c r="D11" t="n">
         <v>677.95</v>
       </c>
       <c r="E11" t="n">
-        <v>677.95</v>
+        <v>678.04</v>
       </c>
     </row>
     <row r="12"/>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2732,8 +2732,60 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-08 17:41:40</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>669.86</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>669.86</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>672.68</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>672.68</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>678.04</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026/09/08 17:41:40</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:45:25</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J44"/>
+  <autoFilter ref="A1:J45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2929,10 +2981,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>677.9725</v>
+        <v>677.986</v>
       </c>
       <c r="D11" t="n">
         <v>677.95</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2784,8 +2784,60 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:51:41</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>669.83</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>669.83</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>672.65</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>672.65</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>678.04</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026/09/08 21:51:41</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:54:46</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J45"/>
+  <autoFilter ref="A1:J46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2981,10 +3033,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>677.986</v>
+        <v>677.995</v>
       </c>
       <c r="D11" t="n">
         <v>677.95</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2836,8 +2836,60 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-09 01:41:42</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>669.82</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>669.82</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>672.64</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>672.64</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>678.04</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026/09/09 01:41:42</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-09-08 17:46:14</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J46"/>
+  <autoFilter ref="A1:J47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2848,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3045,156 +3097,153 @@
         <v>678.04</v>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>678.04</v>
+      </c>
+      <c r="D12" t="n">
+        <v>678.04</v>
+      </c>
+      <c r="E12" t="n">
+        <v>678.04</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3204,19 +3253,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3226,34 +3275,78 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-07 00:00:05</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>677.87</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/09/07 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2026-09-08 02:50:02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>677.95</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-09 01:41:42</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>678.04</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026/09/09 01:41:42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2888,8 +2888,60 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-09 02:50:10</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>669.92</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>669.92</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>672.74</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>672.74</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>678.04</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026/09/09 02:50:10</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-09-08 20:19:47</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J47"/>
+  <autoFilter ref="A1:J48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3104,7 +3156,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>678.04</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2940,8 +2940,60 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-09 05:30:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>669.92</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>669.92</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>672.74</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>672.74</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>678.04</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026/09/09 05:30:00</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-09-08 22:45:57</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J48"/>
+  <autoFilter ref="A1:J49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3156,7 +3208,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
         <v>678.04</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2992,8 +2992,60 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-09 08:29:07</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>669.92</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>669.92</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>672.74</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>672.74</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>678.04</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026/09/09 08:29:07</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-09-09 00:42:40</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J49"/>
+  <autoFilter ref="A1:J50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3208,7 +3260,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
         <v>678.04</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3044,8 +3044,60 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:16:45</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>669.57</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>669.57</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>672.38</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>672.38</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>677.69</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026/09/09 13:16:45</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-09-09 05:20:24</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J50"/>
+  <autoFilter ref="A1:J51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3260,13 +3312,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>678.04</v>
+        <v>677.97</v>
       </c>
       <c r="D12" t="n">
-        <v>678.04</v>
+        <v>677.6900000000001</v>
       </c>
       <c r="E12" t="n">
         <v>678.04</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3096,8 +3096,60 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:51:46</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>669.56</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>669.56</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>672.37</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>672.37</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>677.69</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026/09/09 17:51:46</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:55:57</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J51"/>
+  <autoFilter ref="A1:J52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3312,10 +3364,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>677.97</v>
+        <v>677.9233</v>
       </c>
       <c r="D12" t="n">
         <v>677.6900000000001</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3148,8 +3148,60 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 22:11:47</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>669.47</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>669.47</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>672.28</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>672.28</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>677.69</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026/09/09 22:11:47</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:13:12</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J52"/>
+  <autoFilter ref="A1:J53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3364,10 +3416,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>677.9233</v>
+        <v>677.89</v>
       </c>
       <c r="D12" t="n">
         <v>677.6900000000001</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3200,8 +3200,60 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:46:48</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>669.66</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>669.66</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>672.47</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>672.47</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>677.69</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026/09/10 01:46:48</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:50:54</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J53"/>
+  <autoFilter ref="A1:J54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3212,7 +3264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3428,156 +3480,153 @@
         <v>678.04</v>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>677.6900000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>677.6900000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>677.6900000000001</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3587,19 +3636,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3609,56 +3658,100 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-08 02:50:02</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>677.95</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026/09/08 02:50:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>2026-09-09 01:41:42</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>678.04</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:46:48</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>677.69</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026/09/10 01:46:48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E12"/>
+  <autoFilter ref="A1:E13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3252,8 +3252,60 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-10 02:48:23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>669.77</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>669.77</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>672.58</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>672.58</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>677.69</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026/09/10 02:48:23</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-09-09 20:10:50</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J54"/>
+  <autoFilter ref="A1:J55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3487,7 +3539,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>677.6900000000001</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3304,8 +3304,60 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-10 05:30:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>669.77</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>669.77</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>672.58</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>672.58</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>677.69</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026/09/10 05:30:00</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-09-09 22:33:46</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J55"/>
+  <autoFilter ref="A1:J56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3539,7 +3591,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>677.6900000000001</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3356,8 +3356,60 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-10 07:57:29</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>669.77</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>669.77</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>672.58</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>672.58</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>677.69</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026/09/10 07:57:29</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:33:02</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J56"/>
+  <autoFilter ref="A1:J57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3591,7 +3643,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
         <v>677.6900000000001</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3408,8 +3408,60 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:06:51</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>669.68</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>669.68</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>672.49</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>672.49</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>677.66</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026/09/10 13:06:51</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-09-10 05:12:09</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J57"/>
+  <autoFilter ref="A1:J58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3643,13 +3695,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>677.6900000000001</v>
+        <v>677.684</v>
       </c>
       <c r="D13" t="n">
-        <v>677.6900000000001</v>
+        <v>677.66</v>
       </c>
       <c r="E13" t="n">
         <v>677.6900000000001</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3460,8 +3460,60 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:41:52</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>669.57</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>669.57</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>672.38</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>672.38</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>677.66</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026/09/10 17:41:52</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:47:16</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J58"/>
+  <autoFilter ref="A1:J59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3695,10 +3747,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>677.684</v>
+        <v>677.6799999999999</v>
       </c>
       <c r="D13" t="n">
         <v>677.66</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3512,8 +3512,60 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-10 21:51:53</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>670.11</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>670.11</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>672.93</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>672.93</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>677.66</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026/09/10 21:51:53</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:52:49</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J59"/>
+  <autoFilter ref="A1:J60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3747,10 +3799,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>677.6799999999999</v>
+        <v>677.6771</v>
       </c>
       <c r="D13" t="n">
         <v>677.66</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3564,8 +3564,60 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-11 01:21:54</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>670.1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>670.1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>672.92</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>672.92</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>677.66</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026/09/11 01:21:54</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:26:21</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J60"/>
+  <autoFilter ref="A1:J61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3576,7 +3628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3811,156 +3863,153 @@
         <v>677.6900000000001</v>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>677.66</v>
+      </c>
+      <c r="D14" t="n">
+        <v>677.66</v>
+      </c>
+      <c r="E14" t="n">
+        <v>677.66</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3970,19 +4019,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3992,78 +4041,122 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-09 01:41:42</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>678.04</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026/09/09 01:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>2026-09-10 01:46:48</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>677.69</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-11 01:21:54</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>677.66</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026/09/11 01:21:54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3616,8 +3616,60 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-11 02:54:55</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>670.2</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>670.2</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>673.02</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>673.02</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>677.66</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026/09/11 02:54:55</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:58:15</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J61"/>
+  <autoFilter ref="A1:J62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3870,7 +3922,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>677.66</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3668,8 +3668,60 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-11 05:30:00</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>670.2</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>670.2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>673.02</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>673.02</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>677.66</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026/09/11 05:30:00</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-09-10 22:26:29</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J62"/>
+  <autoFilter ref="A1:J63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3922,7 +3974,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
         <v>677.66</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3720,8 +3720,60 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-11 06:47:21</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>670.2</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>670.2</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>673.02</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>673.02</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>677.66</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026/09/11 06:47:21</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-09-11 00:23:57</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J63"/>
+  <autoFilter ref="A1:J64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3974,7 +4026,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
         <v>677.66</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3772,8 +3772,60 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-11 12:57:01</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>669.91</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>669.91</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>672.73</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>672.73</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026/09/11 12:57:01</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:58:33</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J64"/>
+  <autoFilter ref="A1:J65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4026,13 +4078,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>677.66</v>
+        <v>677.614</v>
       </c>
       <c r="D14" t="n">
-        <v>677.66</v>
+        <v>677.4299999999999</v>
       </c>
       <c r="E14" t="n">
         <v>677.66</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3824,8 +3824,60 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-11 17:26:58</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026/09/11 17:26:58</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:31:33</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J65"/>
+  <autoFilter ref="A1:J66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4078,10 +4130,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>677.614</v>
+        <v>677.5833</v>
       </c>
       <c r="D14" t="n">
         <v>677.4299999999999</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3876,8 +3876,60 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-11 21:41:59</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>669.63</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>669.63</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>672.44</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>672.44</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026/09/11 21:41:59</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:46:48</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J66"/>
+  <autoFilter ref="A1:J67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4130,10 +4182,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>677.5833</v>
+        <v>677.5614</v>
       </c>
       <c r="D14" t="n">
         <v>677.4299999999999</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3928,8 +3928,60 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-12 01:16:59</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>669.64</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>669.64</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>672.45</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>672.45</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026/09/12 01:16:59</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-09-11 17:19:50</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J67"/>
+  <autoFilter ref="A1:J68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3940,7 +3992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4194,156 +4246,153 @@
         <v>677.66</v>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>677.4299999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>677.4299999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>677.4299999999999</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4353,19 +4402,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4375,100 +4424,144 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:46:48</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>677.69</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026/09/10 01:46:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2026-09-11 01:21:54</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>677.66</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-12 01:16:59</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026/09/12 01:16:59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E14"/>
+  <autoFilter ref="A1:E15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3980,8 +3980,60 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-12 02:50:00</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026/09/12 02:50:00</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:51:50</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J68"/>
+  <autoFilter ref="A1:J69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4253,7 +4305,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
         <v>677.4299999999999</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4032,8 +4032,60 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-12 05:30:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026/09/12 05:30:00</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:07:05</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J69"/>
+  <autoFilter ref="A1:J70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4305,7 +4357,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
         <v>677.4299999999999</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4084,8 +4084,60 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:30:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026/09/12 10:30:00</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:43:15</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J70"/>
+  <autoFilter ref="A1:J71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4357,7 +4409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>677.4299999999999</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4136,8 +4136,60 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-13 00:00:05</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026/09/13 00:00:05</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-09-12 17:53:26</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J71"/>
+  <autoFilter ref="A1:J72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4148,7 +4200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4421,156 +4473,153 @@
         <v>677.4299999999999</v>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>677.4299999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>677.4299999999999</v>
+      </c>
+      <c r="E16" t="n">
+        <v>677.4299999999999</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4580,19 +4629,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4602,122 +4651,166 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-11 01:21:54</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>677.66</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026/09/11 01:21:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2026-09-12 01:16:59</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>677.43</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-13 00:00:05</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026/09/13 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E15"/>
+  <autoFilter ref="A1:E16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>